--- a/artfynd/A 61690-2025 artfynd.xlsx
+++ b/artfynd/A 61690-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121196889</v>
+        <v>78378202</v>
       </c>
       <c r="B2" t="n">
-        <v>97279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>102923</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Magleberg, 575 m NO, 150 m OSO torpet, Sk</t>
+          <t>Jularp 1:5, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409717</v>
+        <v>409653</v>
       </c>
       <c r="R2" t="n">
-        <v>6204426</v>
+        <v>6204502</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1946-08-04</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1946-08-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inventerad av Gunnar Olsson</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,21 +763,124 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Rune Stenholm Jakobsen</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Rune Stenholm Jakobsen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121196889</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Magleberg, 575 m NO, 150 m OSO torpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>409717</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6204426</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1946-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1946-08-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
